--- a/design/Элементы.xlsx
+++ b/design/Элементы.xlsx
@@ -11,13 +11,14 @@
     <sheet name="Ресурсы" sheetId="2" r:id="rId2"/>
     <sheet name="Механики" sheetId="3" r:id="rId3"/>
     <sheet name="Базовые черты" sheetId="4" r:id="rId4"/>
+    <sheet name="Действия" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="106">
   <si>
     <t>Сила</t>
   </si>
@@ -308,6 +309,33 @@
   </si>
   <si>
     <t>результат проверки</t>
+  </si>
+  <si>
+    <t>Название действия</t>
+  </si>
+  <si>
+    <t>Движение</t>
+  </si>
+  <si>
+    <t>Описание</t>
+  </si>
+  <si>
+    <t>Перемещение юнита по клеткам тактической карты.</t>
+  </si>
+  <si>
+    <t>Стоимость в ОД/Реакция</t>
+  </si>
+  <si>
+    <t>1 ОД</t>
+  </si>
+  <si>
+    <t>1 Реакция</t>
+  </si>
+  <si>
+    <t>Попытка избежать попадания вражеской атаки.</t>
+  </si>
+  <si>
+    <t>Активный уворот</t>
   </si>
 </sst>
 </file>
@@ -1374,4 +1402,53 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.140625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="18.28515625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" style="9" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="7" customFormat="1" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="61.5" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>104</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>